--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484042_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484042_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. AGUILO RODRIGUEZ</t>
+          <t>J. SERRA CASTILLO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1415</v>
+        <v>3.7178</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1341</v>
+        <v>2.4547</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.9926</v>
+        <v>1.2631</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4624</v>
+        <v>1.6579</v>
       </c>
       <c r="H2" t="n">
-        <v>5.1412</v>
+        <v>1.5983</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.6788</v>
+        <v>0.0597</v>
       </c>
       <c r="J2" t="n">
-        <v>5.7084</v>
+        <v>1.5533</v>
       </c>
       <c r="K2" t="n">
-        <v>5.0659</v>
+        <v>2.1933</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6425999999999999</v>
+        <v>-0.64</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.246</v>
+        <v>0.1046</v>
       </c>
       <c r="N2" t="n">
-        <v>0.07530000000000001</v>
+        <v>-0.5951</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.3214</v>
+        <v>0.6997</v>
       </c>
       <c r="P2" t="n">
-        <v>1.5871</v>
+        <v>2.3806</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5871</v>
+        <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4454</v>
+        <v>0.2112</v>
       </c>
       <c r="T2" t="n">
-        <v>2.1597</v>
+        <v>0.9013</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7141999999999999</v>
+        <v>-0.6902</v>
       </c>
       <c r="V2" t="n">
-        <v>-3.3534</v>
+        <v>-0.532</v>
       </c>
       <c r="W2" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-3.6194</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. SERRA CASTILLO</t>
+          <t>M. AGUILO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3734</v>
+        <v>3.2856</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2506</v>
+        <v>7.2782</v>
       </c>
       <c r="F3" t="n">
-        <v>1.1228</v>
+        <v>-3.9926</v>
       </c>
       <c r="G3" t="n">
-        <v>1.6579</v>
+        <v>4.4624</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5983</v>
+        <v>5.1412</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0597</v>
+        <v>-0.6788</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5533</v>
+        <v>5.7084</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1933</v>
+        <v>5.0659</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.64</v>
+        <v>0.6425999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1046</v>
+        <v>-1.246</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5951</v>
+        <v>0.07530000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>0.6997</v>
+        <v>-1.3214</v>
       </c>
       <c r="P3" t="n">
-        <v>2.3806</v>
+        <v>1.5871</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3806</v>
+        <v>1.5871</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1332</v>
+        <v>0.5895</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6973</v>
+        <v>1.3038</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8305</v>
+        <v>-0.7141999999999999</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.532</v>
+        <v>-3.3534</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.266</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.532</v>
+        <v>-3.6194</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>T. LLOBERA BIBILONI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6386</v>
+        <v>2.1978</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6587</v>
+        <v>1.2341</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9799</v>
+        <v>0.9636</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.7004</v>
+        <v>0.9224</v>
       </c>
       <c r="H4" t="n">
-        <v>0.2625</v>
+        <v>0.434</v>
       </c>
       <c r="I4" t="n">
-        <v>-2.9629</v>
+        <v>0.4884</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.5937</v>
+        <v>1.5685</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6462</v>
+        <v>0.9635</v>
       </c>
       <c r="L4" t="n">
-        <v>-1.2399</v>
+        <v>0.605</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.1067</v>
+        <v>-0.646</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3837</v>
+        <v>-0.5295</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.723</v>
+        <v>-0.1165</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1903</v>
+        <v>0.3968</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1903</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3806</v>
+        <v>1.5871</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1487</v>
+        <v>0.2041</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1768</v>
+        <v>0.856</v>
       </c>
       <c r="U4" t="n">
-        <v>0.972</v>
+        <v>-0.6519</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.6745</v>
       </c>
       <c r="W4" t="n">
-        <v>0.266</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.266</v>
+        <v>0.6745</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>T. LLOBERA BIBILONI</t>
+          <t>J. RIERA MESTRE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1775</v>
+        <v>0.366</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2138</v>
+        <v>-0.878</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9636</v>
+        <v>1.244</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9224</v>
+        <v>-1.2047</v>
       </c>
       <c r="H5" t="n">
-        <v>0.434</v>
+        <v>-0.7861</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4884</v>
+        <v>-0.4186</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5685</v>
+        <v>-1.2258</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9635</v>
+        <v>-0.3926</v>
       </c>
       <c r="L5" t="n">
-        <v>0.605</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.646</v>
+        <v>0.0212</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5295</v>
+        <v>-0.3935</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1165</v>
+        <v>0.4146</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3968</v>
+        <v>0.7935</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1903</v>
+        <v>-0.1984</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5871</v>
+        <v>0.9919</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8162</v>
+        <v>-0.0921</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1643</v>
+        <v>-0.323</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.6519</v>
+        <v>0.2309</v>
       </c>
       <c r="V5" t="n">
-        <v>0.6745</v>
+        <v>0.8692</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X5" t="n">
-        <v>0.6745</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. RIERA MESTRE</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.19</v>
+        <v>-0.0236</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.0821</v>
+        <v>-0.5826</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2721</v>
+        <v>0.5591</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.2047</v>
+        <v>-2.7004</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7861</v>
+        <v>0.2625</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4186</v>
+        <v>-2.9629</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2258</v>
+        <v>-0.5937</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.3926</v>
+        <v>0.6462</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.8332000000000001</v>
+        <v>-1.2399</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0212</v>
+        <v>-2.1067</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3935</v>
+        <v>-0.3837</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4146</v>
+        <v>-1.723</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7935</v>
+        <v>1.1903</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.1984</v>
+        <v>-1.1903</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9919</v>
+        <v>2.3806</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2681</v>
+        <v>1.4865</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5271</v>
+        <v>0.9354</v>
       </c>
       <c r="U6" t="n">
-        <v>0.259</v>
+        <v>0.5511</v>
       </c>
       <c r="V6" t="n">
-        <v>0.8692</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>0.8692</v>
+        <v>0.266</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.0961</v>
+        <v>-0.836</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2599</v>
+        <v>-0.0558</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8362000000000001</v>
+        <v>-0.7801</v>
       </c>
       <c r="G7" t="n">
         <v>-1.3995</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0374</v>
+        <v>0.2976</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0737</v>
+        <v>0.2778</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0363</v>
+        <v>0.0198</v>
       </c>
       <c r="V7" t="n">
         <v>0.266</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.2745</v>
+        <v>-1.16</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.2131</v>
+        <v>-1.9864</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9386</v>
+        <v>0.8264</v>
       </c>
       <c r="G8" t="n">
         <v>-1.1321</v>
@@ -1078,13 +1078,13 @@
         <v>1.3887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2732</v>
+        <v>-0.1587</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4761</v>
+        <v>-0.2493</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2029</v>
+        <v>0.0906</v>
       </c>
       <c r="V8" t="n">
         <v>-0.266</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6327</v>
+        <v>-1.5998</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.28</v>
+        <v>-1.3594</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3526</v>
+        <v>-0.2404</v>
       </c>
       <c r="G9" t="n">
         <v>-0.9861</v>
@@ -1156,13 +1156,13 @@
         <v>1.9838</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8207</v>
+        <v>-0.7879</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0056</v>
+        <v>-0.08500000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.8151</v>
+        <v>-0.7029</v>
       </c>
       <c r="V9" t="n">
         <v>-1.8097</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. CAMÍ GALERA</t>
+          <t>X. ANDREU GARI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2767</v>
+        <v>-1.9404</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.8141</v>
+        <v>-2.0489</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5373</v>
+        <v>0.1086</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1533</v>
+        <v>-2.7113</v>
       </c>
       <c r="H10" t="n">
-        <v>1.5726</v>
+        <v>0.1261</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.7259</v>
+        <v>-2.8373</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1502</v>
+        <v>-1.6522</v>
       </c>
       <c r="K10" t="n">
-        <v>2.2284</v>
+        <v>0.3884</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.0782</v>
+        <v>-2.0406</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3035</v>
+        <v>-1.059</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6558</v>
+        <v>-0.2623</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.7967</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.5952</v>
+        <v>1.3887</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9758</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>2.3806</v>
+        <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.2623</v>
+        <v>-0.6178</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0115</v>
+        <v>-0.3967</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2738</v>
+        <v>-0.2211</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.266</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X. ANDREU GARI</t>
+          <t>P. CAMÍ GALERA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.3417</v>
+        <v>-2.2453</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.338</v>
+        <v>-3.0352</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0037</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.7113</v>
+        <v>-1.1533</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1261</v>
+        <v>1.5726</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.8373</v>
+        <v>-2.7259</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.6522</v>
+        <v>0.1502</v>
       </c>
       <c r="K11" t="n">
-        <v>0.3884</v>
+        <v>2.2284</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0406</v>
+        <v>-2.0782</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.059</v>
+        <v>-1.3035</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.2623</v>
+        <v>-0.6558</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7967</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>1.3887</v>
+        <v>-0.5952</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-2.9758</v>
       </c>
       <c r="R11" t="n">
-        <v>1.3887</v>
+        <v>2.3806</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.0191</v>
+        <v>-0.2309</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.6858</v>
+        <v>-0.2096</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3333</v>
+        <v>-0.0213</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.8076</v>
+        <v>-2.4417</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.5591</v>
+        <v>-1.8846</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2486</v>
+        <v>-0.5572</v>
       </c>
       <c r="G12" t="n">
         <v>-4.1602</v>
@@ -1390,13 +1390,13 @@
         <v>1.5871</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3021</v>
+        <v>0.0638</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5157</v>
+        <v>0.1588</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2136</v>
+        <v>-0.095</v>
       </c>
       <c r="V12" t="n">
         <v>0.266</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.8182</v>
+        <v>-4.1116</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.5727</v>
+        <v>-4.0626</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.2454</v>
+        <v>-0.049</v>
       </c>
       <c r="G13" t="n">
         <v>-5.5111</v>
@@ -1468,13 +1468,13 @@
         <v>2.1822</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0844</v>
+        <v>0.6221</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5726</v>
+        <v>1.0827</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.657</v>
+        <v>-0.4606</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2065</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.7265</v>
+        <v>-4.791200000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>-5.8618</v>
+        <v>-4.926499999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>0.1352000000000003</v>
+        <v>0.1353000000000005</v>
       </c>
       <c r="G14" t="n">
         <v>-13.916</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.154499999999999</v>
+        <v>-1.1545</v>
       </c>
       <c r="I14" t="n">
         <v>-12.7613</v>
@@ -1525,10 +1525,10 @@
         <v>4.771800000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>-8.94</v>
+        <v>-8.940000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.7475</v>
+        <v>-9.747499999999999</v>
       </c>
       <c r="N14" t="n">
         <v>-5.926500000000001</v>
@@ -1546,13 +1546,13 @@
         <v>19.8384</v>
       </c>
       <c r="S14" t="n">
-        <v>0.6521999999999994</v>
+        <v>1.5874</v>
       </c>
       <c r="T14" t="n">
-        <v>3.317</v>
+        <v>4.2522</v>
       </c>
       <c r="U14" t="n">
-        <v>-2.6646</v>
+        <v>-2.6648</v>
       </c>
       <c r="V14" t="n">
         <v>-5.357900000000001</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5456</v>
+        <v>3.7156</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7143</v>
+        <v>3.6123</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.1687</v>
+        <v>0.1034</v>
       </c>
       <c r="G15" t="n">
         <v>2.4869</v>
@@ -1624,13 +1624,13 @@
         <v>0.3968</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.4932</v>
+        <v>-0.3231</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3175</v>
+        <v>0.2154</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8106</v>
+        <v>-0.5386</v>
       </c>
       <c r="V15" t="n">
         <v>2.1469</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3904</v>
+        <v>3.3496</v>
       </c>
       <c r="E16" t="n">
         <v>1.2831</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1073</v>
+        <v>2.0666</v>
       </c>
       <c r="G16" t="n">
         <v>1.7979</v>
@@ -1702,13 +1702,13 @@
         <v>0.9919</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1201</v>
+        <v>0.0793</v>
       </c>
       <c r="T16" t="n">
         <v>0.1418</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0217</v>
+        <v>-0.0625</v>
       </c>
       <c r="V16" t="n">
         <v>1.4724</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. MALO MONTORIO</t>
+          <t>X. ROSÀS MARCO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.1344</v>
+        <v>3.1764</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2516</v>
+        <v>1.3442</v>
       </c>
       <c r="F17" t="n">
-        <v>2.8828</v>
+        <v>1.8322</v>
       </c>
       <c r="G17" t="n">
-        <v>3.9413</v>
+        <v>3.4238</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3124</v>
+        <v>1.4858</v>
       </c>
       <c r="I17" t="n">
-        <v>3.6289</v>
+        <v>1.938</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2763</v>
+        <v>2.9603</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8304</v>
+        <v>2.6613</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4458</v>
+        <v>0.299</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6651</v>
+        <v>0.4635</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.518</v>
+        <v>-1.1755</v>
       </c>
       <c r="O17" t="n">
-        <v>2.1831</v>
+        <v>1.639</v>
       </c>
       <c r="P17" t="n">
-        <v>-4.5628</v>
+        <v>-1.7855</v>
       </c>
       <c r="Q17" t="n">
-        <v>-5.9515</v>
+        <v>-2.9758</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3887</v>
+        <v>1.1903</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8867</v>
+        <v>0.3315</v>
       </c>
       <c r="T17" t="n">
-        <v>2.0577</v>
+        <v>0.1531</v>
       </c>
       <c r="U17" t="n">
-        <v>0.829</v>
+        <v>0.1784</v>
       </c>
       <c r="V17" t="n">
-        <v>0.8692</v>
+        <v>1.2065</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8692</v>
+        <v>1.2065</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. ROSÀS MARCO</t>
+          <t>K. GUILLET</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.9197</v>
+        <v>2.3598</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5279</v>
+        <v>-0.3493</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3918</v>
+        <v>2.7091</v>
       </c>
       <c r="G18" t="n">
-        <v>3.4238</v>
+        <v>1.4898</v>
       </c>
       <c r="H18" t="n">
-        <v>1.4858</v>
+        <v>-0.4289</v>
       </c>
       <c r="I18" t="n">
-        <v>1.938</v>
+        <v>1.9187</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9603</v>
+        <v>0.4215</v>
       </c>
       <c r="K18" t="n">
-        <v>2.6613</v>
+        <v>0.4138</v>
       </c>
       <c r="L18" t="n">
-        <v>0.299</v>
+        <v>0.0077</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4635</v>
+        <v>1.0683</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1755</v>
+        <v>-0.8427</v>
       </c>
       <c r="O18" t="n">
-        <v>1.639</v>
+        <v>1.911</v>
       </c>
       <c r="P18" t="n">
-        <v>-1.7855</v>
+        <v>0.3968</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.9758</v>
+        <v>-0.9919</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1903</v>
+        <v>1.3887</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9251</v>
+        <v>0.4733</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6631</v>
+        <v>0.2212</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.262</v>
+        <v>0.2521</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2065</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. GUILLET</t>
+          <t>J. MALO MONTORIO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.3787</v>
+        <v>1.6151</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5533</v>
+        <v>-0.8707</v>
       </c>
       <c r="F19" t="n">
-        <v>1.932</v>
+        <v>2.4858</v>
       </c>
       <c r="G19" t="n">
-        <v>1.4898</v>
+        <v>3.9413</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4289</v>
+        <v>0.3124</v>
       </c>
       <c r="I19" t="n">
-        <v>1.9187</v>
+        <v>3.6289</v>
       </c>
       <c r="J19" t="n">
-        <v>0.4215</v>
+        <v>3.2763</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4138</v>
+        <v>1.8304</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0077</v>
+        <v>1.4458</v>
       </c>
       <c r="M19" t="n">
-        <v>1.0683</v>
+        <v>0.6651</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8427</v>
+        <v>-1.518</v>
       </c>
       <c r="O19" t="n">
-        <v>1.911</v>
+        <v>2.1831</v>
       </c>
       <c r="P19" t="n">
-        <v>0.3968</v>
+        <v>-4.5628</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9919</v>
+        <v>-5.9515</v>
       </c>
       <c r="R19" t="n">
         <v>1.3887</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5079</v>
+        <v>1.3674</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0171</v>
+        <v>0.9354</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.525</v>
+        <v>0.432</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8692</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. PARDINA CERESUELA</t>
+          <t>A. FERNANDEZ FUERTES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0204</v>
+        <v>0.1428</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0338</v>
+        <v>-0.5058</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0543</v>
+        <v>0.6486</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5566</v>
+        <v>-0.127</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8714</v>
+        <v>-1.1596</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.3148</v>
+        <v>1.0326</v>
       </c>
       <c r="J20" t="n">
-        <v>0.388</v>
+        <v>-0.9921</v>
       </c>
       <c r="K20" t="n">
-        <v>0.3077</v>
+        <v>-1.597</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0803</v>
+        <v>0.605</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1686</v>
+        <v>0.865</v>
       </c>
       <c r="N20" t="n">
-        <v>0.5637</v>
+        <v>0.4374</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.3951</v>
+        <v>0.4276</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.3968</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-0.9919</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>0.5952</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.2398</v>
+        <v>-0.5399</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3798</v>
+        <v>0.0057</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6196</v>
+        <v>-0.5457</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3373</v>
+        <v>1.2065</v>
       </c>
       <c r="W20" t="n">
-        <v>0.266</v>
+        <v>1.4724</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6032</v>
+        <v>-0.266</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. FERNANDEZ FUERTES</t>
+          <t>J. PARDINA CERESUELA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.4617</v>
+        <v>0.0536</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.5058</v>
+        <v>0.7278</v>
       </c>
       <c r="F21" t="n">
-        <v>0.0441</v>
+        <v>-0.6742</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.127</v>
+        <v>0.5566</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1596</v>
+        <v>0.8714</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0326</v>
+        <v>-0.3148</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9921</v>
+        <v>0.388</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.597</v>
+        <v>0.3077</v>
       </c>
       <c r="L21" t="n">
-        <v>0.605</v>
+        <v>0.0803</v>
       </c>
       <c r="M21" t="n">
-        <v>0.865</v>
+        <v>0.1686</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4374</v>
+        <v>0.5637</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4276</v>
+        <v>-0.3951</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.3968</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9919</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5952</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1444</v>
+        <v>-0.1658</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0057</v>
+        <v>0.0737</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.1502</v>
+        <v>-0.2395</v>
       </c>
       <c r="V21" t="n">
-        <v>1.2065</v>
+        <v>-0.3373</v>
       </c>
       <c r="W21" t="n">
-        <v>1.4724</v>
+        <v>0.266</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.266</v>
+        <v>-0.6032</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8594000000000001</v>
+        <v>-1.0932</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3332</v>
+        <v>-0.8433</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5262</v>
+        <v>-0.2499</v>
       </c>
       <c r="G22" t="n">
         <v>0.2086</v>
@@ -2170,13 +2170,13 @@
         <v>0.1984</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.7496</v>
       </c>
       <c r="T22" t="n">
-        <v>0.9977</v>
+        <v>0.4875</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0142</v>
+        <v>0.2621</v>
       </c>
       <c r="V22" t="n">
         <v>-0.266</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.226</v>
+        <v>-1.6181</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1982</v>
+        <v>-0.586</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0278</v>
+        <v>-1.032</v>
       </c>
       <c r="G23" t="n">
         <v>0.7239</v>
@@ -2248,13 +2248,13 @@
         <v>0.3968</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.4223</v>
+        <v>0.1856</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1643</v>
+        <v>0.4478</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.258</v>
+        <v>-0.2622</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9405</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0748</v>
+        <v>-3.2543</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.3554</v>
+        <v>-3.9473</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2807</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G24" t="n">
         <v>-0.586</v>
@@ -2326,13 +2326,13 @@
         <v>0.3968</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.9098000000000001</v>
+        <v>-0.0893</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.4251</v>
+        <v>-0.017</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4847</v>
+        <v>-0.0723</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>5.726500000000001</v>
+        <v>8.4473</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1352000000000011</v>
+        <v>-0.1349999999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>5.8617</v>
+        <v>8.582599999999999</v>
       </c>
       <c r="G25" t="n">
         <v>13.9158</v>
@@ -2383,7 +2383,7 @@
         <v>5.926200000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>3.8212</v>
+        <v>3.821199999999999</v>
       </c>
       <c r="M25" t="n">
         <v>4.1683</v>
@@ -2404,19 +2404,19 @@
         <v>6.9436</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.6523000000000003</v>
+        <v>2.0686</v>
       </c>
       <c r="T25" t="n">
-        <v>2.6648</v>
+        <v>2.6646</v>
       </c>
       <c r="U25" t="n">
-        <v>-3.317</v>
+        <v>-0.5962</v>
       </c>
       <c r="V25" t="n">
-        <v>5.3577</v>
+        <v>5.357699999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>7.290900000000001</v>
+        <v>7.2909</v>
       </c>
       <c r="X25" t="n">
         <v>-1.9332</v>
